--- a/문화정책_라벨링_중앙·서울_코드기준.xlsx
+++ b/문화정책_라벨링_중앙·서울_코드기준.xlsx
@@ -17,7 +17,46 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="755" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="847" uniqueCount="284">
+  <si>
+    <t>판정 기준 (원본 작성안내와 동일)</t>
+  </si>
+  <si>
+    <t>정책 원문(D열)을 읽고 E~F열을 채워주세요.</t>
+  </si>
+  <si>
+    <t>Q1. 이 정책, 청년 개인(또는 청년 창업기업)에게 실제로 돈이 지급되나요?</t>
+  </si>
+  <si>
+    <t>→ 있음 / 없음 / 비율기반 중 선택 (드롭다운)</t>
+  </si>
+  <si>
+    <t>주의사항</t>
+  </si>
+  <si>
+    <t>- 대출/융자/보증 한도는 '없음' (상환해야 하는 돈)</t>
+  </si>
+  <si>
+    <t>- 사업 전체 예산/펀드 조성액은 '없음'</t>
+  </si>
+  <si>
+    <t>- 자격조건의 숫자는 지원금액이 아님</t>
+  </si>
+  <si>
+    <t>- 두 분(라벨러1, 라벨러2)은 독립적으로 판정</t>
+  </si>
+  <si>
+    <t>- '자동판정(참고)' 열은 기계가 채운 초안이므로 정답으로 쓰지 말고 참고만 하세요</t>
+  </si>
+  <si>
+    <t>선별 기준</t>
+  </si>
+  <si>
+    <t>- 온통청년 API 공식 필드 사용: pvsnInstGroupCd 0054001=중앙부처(379건), 서울=지자체 중 zipCd 서울 법정동코드/기관명 서울(69건)</t>
+  </si>
+  <si>
+    <t>- 문화판별: 중분류(문화활동/예술인지원)=엄격 기준 26건 / 대분류에 '문화' 포함(복지문화 등)=넓은 기준, 건강·금융 정책 섞여 있음</t>
+  </si>
   <si>
     <t>번호</t>
   </si>
@@ -52,10 +91,13 @@
     <t>문화판별기준</t>
   </si>
   <si>
-    <t>자동판정(참고)</t>
+    <t>모델자동판정(참고)</t>
   </si>
   <si>
     <t>자동판정(인간)</t>
+  </si>
+  <si>
+    <t>베이스라인자동판정</t>
   </si>
   <si>
     <t>20250827005400211523</t>
@@ -82,10 +124,10 @@
     <t>중분류(문화활동/예술인지원)</t>
   </si>
   <si>
-    <t>없음</t>
-  </si>
-  <si>
     <t>있음</t>
+  </si>
+  <si>
+    <t>확인필요</t>
   </si>
   <si>
     <t>20250827005400211522</t>
@@ -218,6 +260,9 @@
   <si>
     <t>청년예술인과 멘토 역할을 수행할 전문예술인 해외공연(15명 내외)
    - 중국, 일본, 베트남 등 우호협력단체의 교류행사와 연계 추진</t>
+  </si>
+  <si>
+    <t>없음</t>
   </si>
   <si>
     <t>20260504005400113126</t>
@@ -638,9 +683,6 @@
  ㅇ 사업비 : 3,685백만원 (지방비 100%)</t>
   </si>
   <si>
-    <t>확인필요</t>
-  </si>
-  <si>
     <t>20250519005400210850</t>
   </si>
   <si>
@@ -709,9 +751,6 @@
 - 저소득층 : 53%, ㆍ 기초생활보장법에 따른 기초생활수급자 및 차상위계층
 - 2자녀가구 : 30%
 - 3자녀 이상 가구 : 50%</t>
-  </si>
-  <si>
-    <t>비율기반</t>
   </si>
   <si>
     <t>20260605005400113228</t>
@@ -1037,9 +1076,6 @@
 ※ 육아휴직급여(육아휴직수당 포함) 및 군장병급여만 있는 경우, 정부기여금 매칭비율 6% 적용</t>
   </si>
   <si>
-    <t>확인 필요</t>
-  </si>
-  <si>
     <t>20250617005400110946</t>
   </si>
   <si>
@@ -1085,6 +1121,9 @@
 -온라인 발굴, 초기상담 후 고립정도에 적합한 프로그램 제공(자조모임, 심리상담 및 가족관계 회복, 공동생활, 소통기술 습득, 간단한 일경험 등)</t>
   </si>
   <si>
+    <t xml:space="preserve">없음 </t>
+  </si>
+  <si>
     <t>20250609005400110892</t>
   </si>
   <si>
@@ -1092,6 +1131,9 @@
   </si>
   <si>
     <t>자립준비청년에게 매월 자립수당 50만원 현금 지급(본인 명의 계좌 이체)</t>
+  </si>
+  <si>
+    <t>확인 필요</t>
   </si>
   <si>
     <t>20250609005400110890</t>
@@ -1213,53 +1255,19 @@
 -지역 내 중고교·대학 및 병원과 상시체계 협력체계 구축, 의료·돌봄 서비스 신청대행·연계, 연 200만원 자기돌봄비 지급
 - 청년당사자를 위한 민·관 교육 장학금 ,금융, 주거, 법률, 일자리 등 필요한 서비스 연계</t>
   </si>
-  <si>
-    <t>판정 기준 (원본 작성안내와 동일)</t>
-  </si>
-  <si>
-    <t>정책 원문(D열)을 읽고 E~F열을 채워주세요.</t>
-  </si>
-  <si>
-    <t>Q1. 이 정책, 청년 개인(또는 청년 창업기업)에게 실제로 돈이 지급되나요?</t>
-  </si>
-  <si>
-    <t>→ 있음 / 없음 / 비율기반 중 선택 (드롭다운)</t>
-  </si>
-  <si>
-    <t>주의사항</t>
-  </si>
-  <si>
-    <t>- 대출/융자/보증 한도는 '없음' (상환해야 하는 돈)</t>
-  </si>
-  <si>
-    <t>- 사업 전체 예산/펀드 조성액은 '없음'</t>
-  </si>
-  <si>
-    <t>- 자격조건의 숫자는 지원금액이 아님</t>
-  </si>
-  <si>
-    <t>- 두 분(라벨러1, 라벨러2)은 독립적으로 판정</t>
-  </si>
-  <si>
-    <t>- '자동판정(참고)' 열은 기계가 채운 초안이므로 정답으로 쓰지 말고 참고만 하세요</t>
-  </si>
-  <si>
-    <t>선별 기준</t>
-  </si>
-  <si>
-    <t>- 온통청년 API 공식 필드 사용: pvsnInstGroupCd 0054001=중앙부처(379건), 서울=지자체 중 zipCd 서울 법정동코드/기관명 서울(69건)</t>
-  </si>
-  <si>
-    <t>- 문화판별: 중분류(문화활동/예술인지원)=엄격 기준 26건 / 대분류에 '문화' 포함(복지문화 등)=넓은 기준, 건강·금융 정책 섞여 있음</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="4">
     <font>
       <sz val="11.0"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <color theme="1"/>
       <name val="Calibri"/>
       <scheme val="minor"/>
@@ -1271,12 +1279,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <scheme val="minor"/>
+      <sz val="11.0"/>
+      <color rgb="FF000000"/>
+      <name val="&quot;맑은 고딕&quot;"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1285,46 +1293,143 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD9E1F2"/>
-        <bgColor rgb="FFD9E1F2"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
+        <fgColor rgb="FFB7E1CD"/>
+        <bgColor rgb="FFB7E1CD"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6F8F9"/>
+        <bgColor rgb="FFF6F8F9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD0E0E3"/>
+        <bgColor rgb="FFD0E0E3"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border/>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="14">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
-    <xf borderId="1" fillId="2" fontId="1" numFmtId="0" xfId="0" applyBorder="1" applyFill="1" applyFont="1"/>
-    <xf borderId="1" fillId="3" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="4" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="2" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle xfId="0" name="Normal" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="5">
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="none"/>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF356854"/>
+          <bgColor rgb="FF356854"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFFFF"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <font/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF6F8F9"/>
+          <bgColor rgb="FFF6F8F9"/>
+        </patternFill>
+      </fill>
+      <border/>
+    </dxf>
+    <dxf>
+      <border>
+        <left style="thin">
+          <color rgb="FF356854"/>
+        </left>
+        <right style="thin">
+          <color rgb="FF356854"/>
+        </right>
+        <top style="thin">
+          <color rgb="FF356854"/>
+        </top>
+        <bottom style="thin">
+          <color rgb="FF356854"/>
+        </bottom>
+      </border>
+    </dxf>
+  </dxfs>
+  <tableStyles count="1">
+    <tableStyle count="4" pivot="0" name="문화_라벨링-style">
+      <tableStyleElement dxfId="1" type="headerRow"/>
+      <tableStyleElement dxfId="2" type="firstRowStripe"/>
+      <tableStyleElement dxfId="3" type="secondRowStripe"/>
+      <tableStyleElement dxfId="4" size="0" type="wholeTable"/>
+    </tableStyle>
+  </tableStyles>
 </styleSheet>
 </file>
 
@@ -1334,6 +1439,28 @@
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:N82" displayName="표1" name="표1" id="1">
+  <tableColumns count="14">
+    <tableColumn name="번호" id="1"/>
+    <tableColumn name="정책번호" id="2"/>
+    <tableColumn name="정책명" id="3"/>
+    <tableColumn name="정책지원내용(원문)" id="4"/>
+    <tableColumn name="라벨러1_판정" id="5"/>
+    <tableColumn name="라벨러2_판정" id="6"/>
+    <tableColumn name="비고" id="7"/>
+    <tableColumn name="구분" id="8"/>
+    <tableColumn name="대분류" id="9"/>
+    <tableColumn name="중분류" id="10"/>
+    <tableColumn name="문화판별기준" id="11"/>
+    <tableColumn name="모델자동판정(참고)" id="12"/>
+    <tableColumn name="자동판정(인간)" id="13"/>
+    <tableColumn name="베이스라인자동판정" id="14"/>
+  </tableColumns>
+  <tableStyleInfo name="문화_라벨링-style" showColumnStripes="0" showFirstColumn="1" showLastColumn="1" showRowStripes="1"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1538,2842 +1665,3216 @@
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
     <col customWidth="1" min="1" max="1" width="6.0"/>
-    <col customWidth="1" min="2" max="2" width="22.0"/>
-    <col customWidth="1" min="3" max="3" width="38.0"/>
-    <col customWidth="1" min="4" max="4" width="60.0"/>
-    <col customWidth="1" min="5" max="6" width="12.0"/>
+    <col customWidth="1" min="2" max="2" width="25.86"/>
+    <col customWidth="1" min="3" max="4" width="43.0"/>
+    <col customWidth="1" min="5" max="6" width="22.0"/>
     <col customWidth="1" min="7" max="7" width="16.0"/>
-    <col customWidth="1" min="8" max="8" width="10.0"/>
-    <col customWidth="1" min="9" max="9" width="14.0"/>
-    <col customWidth="1" min="10" max="10" width="20.0"/>
-    <col customWidth="1" min="11" max="11" width="24.0"/>
-    <col customWidth="1" min="12" max="12" width="18.29"/>
+    <col customWidth="1" min="8" max="8" width="10.29"/>
+    <col customWidth="1" min="9" max="9" width="16.29"/>
+    <col customWidth="1" min="10" max="10" width="21.14"/>
+    <col customWidth="1" min="11" max="11" width="27.71"/>
+    <col customWidth="1" min="12" max="12" width="23.14"/>
     <col customWidth="1" min="13" max="13" width="19.86"/>
-    <col customWidth="1" min="14" max="26" width="8.71"/>
+    <col customWidth="1" min="14" max="14" width="23.29"/>
+    <col customWidth="1" min="15" max="26" width="8.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="42.75" customHeight="1">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="3">
+      <c r="A1" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L1" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="M1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="N1" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" ht="22.5" customHeight="1">
+      <c r="A2" s="4">
         <v>1.0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3"/>
-      <c r="H2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M2" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="3">
+      <c r="B2" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="H2" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N2" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" ht="22.5" customHeight="1">
+      <c r="A3" s="4">
         <v>2.0</v>
       </c>
-      <c r="B3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3">
+      <c r="B3" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="5"/>
+      <c r="F3" s="5"/>
+      <c r="H3" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J3" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N3" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="4" ht="22.5" customHeight="1">
+      <c r="A4" s="4">
         <v>3.0</v>
       </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3"/>
-      <c r="H4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3">
+      <c r="B4" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="5"/>
+      <c r="H4" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J4" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M4" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="5" ht="22.5" customHeight="1">
+      <c r="A5" s="4">
         <v>4.0</v>
       </c>
-      <c r="B5" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="3" t="s">
+      <c r="B5" s="4" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="5"/>
+      <c r="H5" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3"/>
-      <c r="H5" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J5" s="3" t="s">
+      <c r="I5" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K5" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3">
+      <c r="J5" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N5" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="6" ht="22.5" customHeight="1">
+      <c r="A6" s="4">
         <v>5.0</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="H6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J6" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="M6" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="7" ht="22.5" customHeight="1">
+      <c r="A7" s="4">
+        <v>6.0</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="5"/>
+      <c r="H7" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J7" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="K7" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="E6" s="3"/>
-      <c r="F6" s="3"/>
-      <c r="H6" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J6" s="3" t="s">
+      <c r="L7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M7" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" ht="22.5" customHeight="1">
+      <c r="A8" s="4">
+        <v>7.0</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="5"/>
+      <c r="H8" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I8" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K6" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3">
-        <v>6.0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="J8" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M8" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3"/>
-      <c r="H7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3">
-        <v>7.0</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E8" s="3"/>
-      <c r="F8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3">
+    </row>
+    <row r="9" ht="22.5" customHeight="1">
+      <c r="A9" s="4">
         <v>8.0</v>
       </c>
-      <c r="B9" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3"/>
-      <c r="H9" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I9" s="3" t="s">
+      <c r="B9" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="E9" s="5"/>
+      <c r="F9" s="5"/>
+      <c r="H9" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M9" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" ht="22.5" customHeight="1">
+      <c r="A10" s="4">
+        <v>9.0</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="E10" s="5"/>
+      <c r="F10" s="5"/>
+      <c r="H10" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M10" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="11" ht="22.5" customHeight="1">
+      <c r="A11" s="4">
+        <v>10.0</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E11" s="5"/>
+      <c r="F11" s="5"/>
+      <c r="H11" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M11" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="12" ht="22.5" customHeight="1">
+      <c r="A12" s="4">
+        <v>11.0</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="E12" s="5"/>
+      <c r="F12" s="5"/>
+      <c r="H12" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K12" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M12" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="13" ht="22.5" customHeight="1">
+      <c r="A13" s="4">
+        <v>12.0</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="5"/>
+      <c r="H13" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K13" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M13" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="14" ht="22.5" customHeight="1">
+      <c r="A14" s="4">
+        <v>13.0</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="5"/>
+      <c r="H14" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K14" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L14" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M14" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="15" ht="22.5" customHeight="1">
+      <c r="A15" s="4">
+        <v>14.0</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+      <c r="H15" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K15" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M15" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="16" ht="22.5" customHeight="1">
+      <c r="A16" s="4">
+        <v>15.0</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="5"/>
+      <c r="H16" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K16" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M16" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17" ht="22.5" customHeight="1">
+      <c r="A17" s="4">
+        <v>16.0</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
+      <c r="H17" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L17" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M17" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="18" ht="22.5" customHeight="1">
+      <c r="A18" s="4">
+        <v>17.0</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="E18" s="5"/>
+      <c r="F18" s="5"/>
+      <c r="H18" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K18" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M18" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="19" ht="22.5" customHeight="1">
+      <c r="A19" s="4">
+        <v>18.0</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="E19" s="5"/>
+      <c r="F19" s="5"/>
+      <c r="H19" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K19" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M19" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="20" ht="22.5" customHeight="1">
+      <c r="A20" s="4">
+        <v>19.0</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="E20" s="5"/>
+      <c r="F20" s="5"/>
+      <c r="H20" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M20" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="21" ht="15.75" customHeight="1">
+      <c r="A21" s="4">
+        <v>20.0</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="E21" s="5"/>
+      <c r="F21" s="5"/>
+      <c r="H21" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="K21" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M21" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" ht="15.75" customHeight="1">
+      <c r="A22" s="4">
+        <v>21.0</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="E22" s="5"/>
+      <c r="F22" s="5"/>
+      <c r="H22" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I22" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J22" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="K22" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M22" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N22" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" ht="15.75" customHeight="1">
+      <c r="A23" s="4">
+        <v>22.0</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="5"/>
+      <c r="H23" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I23" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3">
-        <v>9.0</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="E10" s="3"/>
-      <c r="F10" s="3"/>
-      <c r="H10" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I10" s="3" t="s">
+      <c r="J23" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K23" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L23" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M23" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="N23" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" ht="15.75" customHeight="1">
+      <c r="A24" s="4">
+        <v>23.0</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="5"/>
+      <c r="H24" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J24" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K24" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M24" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N24" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1">
+      <c r="A25" s="4">
+        <v>24.0</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="5"/>
+      <c r="H25" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I25" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K10" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3">
-        <v>10.0</v>
-      </c>
-      <c r="B11" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="H11" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I11" s="3" t="s">
+      <c r="J25" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3">
-        <v>11.0</v>
-      </c>
-      <c r="B12" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="3"/>
-      <c r="F12" s="3"/>
-      <c r="H12" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3">
-        <v>12.0</v>
-      </c>
-      <c r="B13" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="C13" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="D13" s="3" t="s">
+      <c r="K25" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M25" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N25" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" ht="15.75" customHeight="1">
+      <c r="A26" s="4">
+        <v>25.0</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="5"/>
+      <c r="H26" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="3"/>
-      <c r="H13" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I13" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3">
-        <v>13.0</v>
-      </c>
-      <c r="B14" s="3" t="s">
+      <c r="I26" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M26" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N26" s="7" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" ht="15.75" customHeight="1">
+      <c r="A27" s="4">
+        <v>26.0</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="5"/>
+      <c r="H27" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K27" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="L27" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M27" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N27" s="7" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="28" ht="15.75" customHeight="1">
+      <c r="A28" s="4">
+        <v>27.0</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" s="5"/>
+      <c r="F28" s="5"/>
+      <c r="H28" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K28" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M28" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N28" s="7" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="29" ht="15.75" customHeight="1">
+      <c r="A29" s="4">
+        <v>28.0</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="E29" s="5"/>
+      <c r="F29" s="5"/>
+      <c r="H29" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K29" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L29" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="M29" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="N29" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q29" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1">
+      <c r="A30" s="4">
+        <v>29.0</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="E30" s="5"/>
+      <c r="F30" s="5"/>
+      <c r="H30" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K30" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L30" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M30" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N30" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q30" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="31" ht="15.75" customHeight="1">
+      <c r="A31" s="4">
+        <v>30.0</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="E31" s="5"/>
+      <c r="F31" s="5"/>
+      <c r="H31" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K31" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L31" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M31" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N31" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q31" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="32" ht="15.75" customHeight="1">
+      <c r="A32" s="4">
+        <v>31.0</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="5"/>
+      <c r="H32" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L32" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M32" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N32" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q32" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="33" ht="15.75" customHeight="1">
+      <c r="A33" s="4">
+        <v>32.0</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="D33" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="5"/>
+      <c r="H33" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K33" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L33" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M33" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N33" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q33" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="34" ht="15.75" customHeight="1">
+      <c r="A34" s="4">
+        <v>33.0</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="5"/>
+      <c r="H34" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K34" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L34" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M34" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N34" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q34" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" ht="15.75" customHeight="1">
+      <c r="A35" s="4">
+        <v>34.0</v>
+      </c>
+      <c r="B35" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="5"/>
+      <c r="H35" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I35" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J35" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K35" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L35" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M35" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N35" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q35" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="36" ht="15.75" customHeight="1">
+      <c r="A36" s="4">
+        <v>35.0</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="5"/>
+      <c r="H36" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I36" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J36" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K36" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L36" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M36" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N36" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q36" s="11" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="37" ht="15.75" customHeight="1">
+      <c r="A37" s="4">
+        <v>36.0</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="H37" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I37" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J37" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K37" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L37" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="M37" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="N37" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q37" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="38" ht="15.75" customHeight="1">
+      <c r="A38" s="4">
+        <v>37.0</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="E38" s="5"/>
+      <c r="F38" s="5"/>
+      <c r="H38" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I38" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J38" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K38" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L38" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M38" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N38" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q38" s="11" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="39" ht="15.75" customHeight="1">
+      <c r="A39" s="4">
+        <v>38.0</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>153</v>
+      </c>
+      <c r="E39" s="5"/>
+      <c r="F39" s="5"/>
+      <c r="H39" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I39" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J39" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K39" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L39" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M39" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N39" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q39" s="11"/>
+    </row>
+    <row r="40" ht="15.75" customHeight="1">
+      <c r="A40" s="4">
+        <v>39.0</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E40" s="5"/>
+      <c r="F40" s="5"/>
+      <c r="H40" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="I40" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J40" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K40" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L40" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M40" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N40" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q40" s="11"/>
+    </row>
+    <row r="41" ht="15.75" customHeight="1">
+      <c r="A41" s="4">
+        <v>40.0</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="D41" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="E41" s="5"/>
+      <c r="F41" s="5"/>
+      <c r="H41" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I41" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="C14" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-      <c r="H14" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M14" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3">
-        <v>14.0</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-      <c r="H15" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3">
-        <v>15.0</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="H16" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M16" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3">
-        <v>16.0</v>
-      </c>
-      <c r="B17" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="H17" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M17" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3">
-        <v>17.0</v>
-      </c>
-      <c r="B18" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="E18" s="3"/>
-      <c r="F18" s="3"/>
-      <c r="H18" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I18" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M18" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3">
-        <v>18.0</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="E19" s="3"/>
-      <c r="F19" s="3"/>
-      <c r="H19" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I19" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M19" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3">
-        <v>19.0</v>
-      </c>
-      <c r="B20" s="3" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="E20" s="3"/>
-      <c r="F20" s="3"/>
-      <c r="H20" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I20" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J20" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K20" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M20" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="3">
-        <v>20.0</v>
-      </c>
-      <c r="B21" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="E21" s="3"/>
-      <c r="F21" s="3"/>
-      <c r="H21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I21" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J21" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="K21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L21" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M21" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="3">
-        <v>21.0</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E22" s="3"/>
-      <c r="F22" s="3"/>
-      <c r="H22" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I22" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J22" s="3" t="s">
+      <c r="J41" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K41" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L41" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M41" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N41" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q41" s="11"/>
+    </row>
+    <row r="42" ht="15.75" customHeight="1">
+      <c r="A42" s="4">
+        <v>41.0</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D42" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="E42" s="5"/>
+      <c r="F42" s="5"/>
+      <c r="H42" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I42" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J42" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K42" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L42" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M42" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N42" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q42" s="11"/>
+    </row>
+    <row r="43" ht="15.75" customHeight="1">
+      <c r="A43" s="4">
+        <v>42.0</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="E43" s="5"/>
+      <c r="F43" s="5"/>
+      <c r="H43" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I43" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J43" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K43" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L43" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M43" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N43" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q43" s="11"/>
+    </row>
+    <row r="44" ht="15.75" customHeight="1">
+      <c r="A44" s="4">
+        <v>43.0</v>
+      </c>
+      <c r="B44" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E44" s="5"/>
+      <c r="F44" s="5"/>
+      <c r="H44" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I44" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J44" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K44" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L44" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M44" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N44" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q44" s="11"/>
+    </row>
+    <row r="45" ht="15.75" customHeight="1">
+      <c r="A45" s="4">
+        <v>44.0</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D45" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="E45" s="5"/>
+      <c r="F45" s="5"/>
+      <c r="H45" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I45" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J45" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K45" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L45" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M45" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N45" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q45" s="11"/>
+    </row>
+    <row r="46" ht="15.75" customHeight="1">
+      <c r="A46" s="4">
+        <v>45.0</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="D46" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="E46" s="5"/>
+      <c r="F46" s="5"/>
+      <c r="H46" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I46" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J46" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K46" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L46" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M46" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N46" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q46" s="11"/>
+    </row>
+    <row r="47" ht="15.75" customHeight="1">
+      <c r="A47" s="4">
+        <v>46.0</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="D47" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E47" s="5"/>
+      <c r="F47" s="5"/>
+      <c r="H47" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I47" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J47" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K47" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L47" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M47" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N47" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q47" s="11"/>
+    </row>
+    <row r="48" ht="15.75" customHeight="1">
+      <c r="A48" s="4">
+        <v>47.0</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="E48" s="5"/>
+      <c r="F48" s="5"/>
+      <c r="H48" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I48" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J48" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K48" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L48" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M48" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N48" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q48" s="11"/>
+    </row>
+    <row r="49" ht="15.75" customHeight="1">
+      <c r="A49" s="4">
+        <v>48.0</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" s="5"/>
+      <c r="F49" s="5"/>
+      <c r="H49" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I49" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J49" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K49" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L49" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M49" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N49" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q49" s="11"/>
+    </row>
+    <row r="50" ht="15.75" customHeight="1">
+      <c r="A50" s="4">
+        <v>49.0</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="E50" s="5"/>
+      <c r="F50" s="5"/>
+      <c r="H50" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I50" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J50" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K50" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L50" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M50" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N50" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q50" s="11"/>
+    </row>
+    <row r="51" ht="15.75" customHeight="1">
+      <c r="A51" s="4">
+        <v>50.0</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="D51" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="E51" s="5"/>
+      <c r="F51" s="5"/>
+      <c r="H51" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I51" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J51" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K51" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L51" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M51" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N51" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q51" s="11"/>
+    </row>
+    <row r="52" ht="15.75" customHeight="1">
+      <c r="A52" s="4">
+        <v>51.0</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>191</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="H52" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I52" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J52" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K52" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L52" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M52" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N52" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q52" s="11"/>
+    </row>
+    <row r="53" ht="15.75" customHeight="1">
+      <c r="A53" s="4">
+        <v>52.0</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="D53" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="E53" s="5"/>
+      <c r="F53" s="5"/>
+      <c r="H53" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I53" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J53" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K53" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L53" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M53" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N53" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q53" s="11"/>
+    </row>
+    <row r="54" ht="15.75" customHeight="1">
+      <c r="A54" s="4">
+        <v>53.0</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="D54" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E54" s="5"/>
+      <c r="F54" s="5"/>
+      <c r="H54" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I54" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J54" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K54" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L54" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M54" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N54" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q54" s="11"/>
+    </row>
+    <row r="55" ht="15.75" customHeight="1">
+      <c r="A55" s="4">
+        <v>54.0</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E55" s="5"/>
+      <c r="F55" s="5"/>
+      <c r="H55" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I55" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J55" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K55" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L55" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M55" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N55" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q55" s="11"/>
+    </row>
+    <row r="56" ht="15.75" customHeight="1">
+      <c r="A56" s="4">
+        <v>55.0</v>
+      </c>
+      <c r="B56" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="D56" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="E56" s="5"/>
+      <c r="F56" s="5"/>
+      <c r="H56" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I56" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J56" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K56" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L56" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M56" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N56" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q56" s="11"/>
+    </row>
+    <row r="57" ht="15.75" customHeight="1">
+      <c r="A57" s="4">
+        <v>56.0</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>206</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="E57" s="5"/>
+      <c r="F57" s="5"/>
+      <c r="H57" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I57" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J57" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K57" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L57" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M57" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N57" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q57" s="11"/>
+    </row>
+    <row r="58" ht="15.75" customHeight="1">
+      <c r="A58" s="4">
+        <v>57.0</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D58" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="E58" s="5"/>
+      <c r="F58" s="5"/>
+      <c r="H58" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I58" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="J58" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K58" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L58" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M58" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N58" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q58" s="11"/>
+    </row>
+    <row r="59" ht="15.75" customHeight="1">
+      <c r="A59" s="4">
+        <v>58.0</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>212</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="H59" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I59" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K22" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M22" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="3">
-        <v>22.0</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E23" s="3"/>
-      <c r="F23" s="3"/>
-      <c r="H23" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I23" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M23" s="4" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="3">
-        <v>23.0</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="E24" s="3"/>
-      <c r="F24" s="3"/>
-      <c r="H24" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I24" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J24" s="3" t="s">
+      <c r="J59" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K59" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L59" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M59" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N59" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q59" s="11"/>
+    </row>
+    <row r="60" ht="15.75" customHeight="1">
+      <c r="A60" s="4">
+        <v>59.0</v>
+      </c>
+      <c r="B60" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="D60" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="E60" s="5"/>
+      <c r="F60" s="5"/>
+      <c r="H60" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I60" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K24" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M24" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="3">
-        <v>24.0</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="C25" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="D25" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="E25" s="3"/>
-      <c r="F25" s="3"/>
-      <c r="H25" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I25" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J25" s="3" t="s">
+      <c r="J60" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K60" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L60" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M60" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N60" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q60" s="11"/>
+    </row>
+    <row r="61" ht="15.75" customHeight="1">
+      <c r="A61" s="4">
+        <v>60.0</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>218</v>
+      </c>
+      <c r="D61" s="4" t="s">
+        <v>219</v>
+      </c>
+      <c r="E61" s="5"/>
+      <c r="F61" s="5"/>
+      <c r="H61" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I61" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="K25" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M25" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="3">
-        <v>25.0</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="C26" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="E26" s="3"/>
-      <c r="F26" s="3"/>
-      <c r="H26" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I26" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K26" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L26" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M26" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="3">
-        <v>26.0</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="C27" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E27" s="3"/>
-      <c r="F27" s="3"/>
-      <c r="H27" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I27" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="K27" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="L27" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M27" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="3">
-        <v>27.0</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="C28" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="D28" s="3" t="s">
-        <v>102</v>
-      </c>
-      <c r="E28" s="3"/>
-      <c r="F28" s="3"/>
-      <c r="H28" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I28" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M28" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="3">
-        <v>28.0</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="C29" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="D29" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="E29" s="3"/>
-      <c r="F29" s="3"/>
-      <c r="H29" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M29" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="3">
-        <v>29.0</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="C30" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="D30" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="H30" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I30" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M30" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="3">
-        <v>30.0</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="C31" s="3" t="s">
-        <v>112</v>
-      </c>
-      <c r="D31" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E31" s="3"/>
-      <c r="F31" s="3"/>
-      <c r="H31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I31" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M31" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="3">
-        <v>31.0</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="C32" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="3"/>
-      <c r="F32" s="3"/>
-      <c r="H32" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I32" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K32" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L32" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M32" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="3">
-        <v>32.0</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>117</v>
-      </c>
-      <c r="C33" s="3" t="s">
+      <c r="J61" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="K61" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E33" s="3"/>
-      <c r="F33" s="3"/>
-      <c r="H33" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K33" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M33" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="3">
-        <v>33.0</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E34" s="3"/>
-      <c r="F34" s="3"/>
-      <c r="H34" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K34" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M34" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="3">
-        <v>34.0</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>124</v>
-      </c>
-      <c r="C35" s="3" t="s">
-        <v>125</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>126</v>
-      </c>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
-      <c r="H35" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I35" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J35" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K35" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M35" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="3">
-        <v>35.0</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>127</v>
-      </c>
-      <c r="C36" s="3" t="s">
-        <v>128</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>129</v>
-      </c>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="H36" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I36" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J36" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K36" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M36" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="3">
-        <v>36.0</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>130</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>131</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>132</v>
-      </c>
-      <c r="E37" s="3"/>
-      <c r="F37" s="3"/>
-      <c r="H37" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I37" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J37" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K37" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M37" s="4" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="3">
-        <v>37.0</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="C38" s="3" t="s">
+      <c r="L61" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="M61" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="N61" s="7" t="s">
+        <v>34</v>
+      </c>
+      <c r="Q61" s="11"/>
+    </row>
+    <row r="62" ht="15.75" customHeight="1">
+      <c r="A62" s="4">
+        <v>61.0</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>220</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="D62" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="E62" s="5"/>
+      <c r="F62" s="5"/>
+      <c r="H62" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I62" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J62" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="E38" s="3"/>
-      <c r="F38" s="3"/>
-      <c r="H38" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I38" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J38" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L38" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M38" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="3">
-        <v>38.0</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="C39" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="D39" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="E39" s="3"/>
-      <c r="F39" s="3"/>
-      <c r="H39" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K39" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L39" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M39" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="3">
-        <v>39.0</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="C40" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="D40" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="E40" s="3"/>
-      <c r="F40" s="3"/>
-      <c r="H40" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I40" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J40" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K40" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L40" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M40" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="3">
-        <v>40.0</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="C41" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D41" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="E41" s="3"/>
-      <c r="F41" s="3"/>
-      <c r="H41" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I41" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K41" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L41" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M41" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="3">
-        <v>41.0</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="E42" s="3"/>
-      <c r="F42" s="3"/>
-      <c r="H42" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I42" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J42" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K42" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L42" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M42" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="3">
-        <v>42.0</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="C43" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="D43" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="E43" s="3"/>
-      <c r="F43" s="3"/>
-      <c r="H43" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I43" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J43" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M43" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="3">
-        <v>43.0</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="C44" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>155</v>
-      </c>
-      <c r="E44" s="3"/>
-      <c r="F44" s="3"/>
-      <c r="H44" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I44" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J44" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K44" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L44" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M44" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="3">
-        <v>44.0</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>156</v>
-      </c>
-      <c r="C45" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="D45" s="3" t="s">
-        <v>158</v>
-      </c>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="H45" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I45" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J45" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K45" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L45" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M45" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="3">
-        <v>45.0</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="C46" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="D46" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="H46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I46" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J46" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K46" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L46" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M46" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="3">
-        <v>46.0</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="C47" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D47" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="H47" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I47" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K47" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L47" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M47" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="3">
-        <v>47.0</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="C48" s="3" t="s">
-        <v>166</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="H48" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I48" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J48" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M48" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="3">
-        <v>48.0</v>
-      </c>
-      <c r="B49" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="C49" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="D49" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="E49" s="3"/>
-      <c r="F49" s="3"/>
-      <c r="H49" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I49" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J49" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K49" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L49" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M49" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="3">
-        <v>49.0</v>
-      </c>
-      <c r="B50" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="C50" s="3" t="s">
-        <v>172</v>
-      </c>
-      <c r="D50" s="3" t="s">
-        <v>173</v>
-      </c>
-      <c r="E50" s="3"/>
-      <c r="F50" s="3"/>
-      <c r="H50" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I50" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J50" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K50" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L50" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M50" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="3">
-        <v>50.0</v>
-      </c>
-      <c r="B51" s="3" t="s">
-        <v>174</v>
-      </c>
-      <c r="C51" s="3" t="s">
-        <v>175</v>
-      </c>
-      <c r="D51" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="H51" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I51" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J51" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K51" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L51" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M51" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="3">
-        <v>51.0</v>
-      </c>
-      <c r="B52" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="D52" s="3" t="s">
-        <v>179</v>
-      </c>
-      <c r="E52" s="3"/>
-      <c r="F52" s="3"/>
-      <c r="H52" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I52" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J52" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K52" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L52" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M52" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="3">
-        <v>52.0</v>
-      </c>
-      <c r="B53" s="3" t="s">
-        <v>180</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="D53" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="E53" s="3"/>
-      <c r="F53" s="3"/>
-      <c r="H53" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I53" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J53" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L53" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M53" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="3">
-        <v>53.0</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="D54" s="3" t="s">
-        <v>185</v>
-      </c>
-      <c r="E54" s="3"/>
-      <c r="F54" s="3"/>
-      <c r="H54" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I54" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J54" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K54" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L54" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M54" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="3">
-        <v>54.0</v>
-      </c>
-      <c r="B55" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="C55" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D55" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="E55" s="3"/>
-      <c r="F55" s="3"/>
-      <c r="H55" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I55" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J55" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K55" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L55" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M55" s="4" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="3">
-        <v>55.0</v>
-      </c>
-      <c r="B56" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="C56" s="3" t="s">
-        <v>190</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="E56" s="3"/>
-      <c r="F56" s="3"/>
-      <c r="H56" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I56" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J56" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K56" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L56" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M56" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="3">
-        <v>56.0</v>
-      </c>
-      <c r="B57" s="3" t="s">
-        <v>192</v>
-      </c>
-      <c r="C57" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="D57" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="E57" s="3"/>
-      <c r="F57" s="3"/>
-      <c r="H57" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I57" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J57" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K57" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L57" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M57" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="3">
-        <v>57.0</v>
-      </c>
-      <c r="B58" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="E58" s="3"/>
-      <c r="F58" s="3"/>
-      <c r="H58" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I58" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="J58" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K58" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L58" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M58" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="3">
-        <v>58.0</v>
-      </c>
-      <c r="B59" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="C59" s="3" t="s">
-        <v>199</v>
-      </c>
-      <c r="D59" s="3" t="s">
+      <c r="K62" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L62" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M62" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N62" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q62" s="11"/>
+    </row>
+    <row r="63" ht="15.75" customHeight="1">
+      <c r="A63" s="4">
+        <v>62.0</v>
+      </c>
+      <c r="B63" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="D63" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="E63" s="5"/>
+      <c r="F63" s="5"/>
+      <c r="H63" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I63" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J63" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K63" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L63" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M63" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N63" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q63" s="11"/>
+    </row>
+    <row r="64" ht="15.75" customHeight="1">
+      <c r="A64" s="4">
+        <v>63.0</v>
+      </c>
+      <c r="B64" s="4" t="s">
+        <v>226</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>227</v>
+      </c>
+      <c r="D64" s="4" t="s">
+        <v>228</v>
+      </c>
+      <c r="E64" s="5"/>
+      <c r="F64" s="5"/>
+      <c r="H64" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I64" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J64" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K64" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L64" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M64" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N64" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q64" s="11"/>
+    </row>
+    <row r="65" ht="15.75" customHeight="1">
+      <c r="A65" s="4">
+        <v>64.0</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>229</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>230</v>
+      </c>
+      <c r="D65" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="E65" s="5"/>
+      <c r="F65" s="5"/>
+      <c r="H65" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I65" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J65" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K65" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M65" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N65" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q65" s="11"/>
+    </row>
+    <row r="66" ht="15.75" customHeight="1">
+      <c r="A66" s="4">
+        <v>65.0</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="E66" s="5"/>
+      <c r="F66" s="5"/>
+      <c r="H66" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I66" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J66" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K66" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L66" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M66" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N66" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q66" s="11"/>
+    </row>
+    <row r="67" ht="15.75" customHeight="1">
+      <c r="A67" s="4">
+        <v>66.0</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>236</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="E67" s="5"/>
+      <c r="F67" s="5"/>
+      <c r="H67" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I67" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J67" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K67" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="M67" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="N67" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q67" s="11"/>
+    </row>
+    <row r="68" ht="15.75" customHeight="1">
+      <c r="A68" s="4">
+        <v>67.0</v>
+      </c>
+      <c r="B68" s="4" t="s">
+        <v>238</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>239</v>
+      </c>
+      <c r="D68" s="4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E68" s="5"/>
+      <c r="F68" s="5"/>
+      <c r="H68" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I68" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J68" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K68" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L68" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M68" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N68" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q68" s="11"/>
+    </row>
+    <row r="69" ht="15.75" customHeight="1">
+      <c r="A69" s="4">
+        <v>68.0</v>
+      </c>
+      <c r="B69" s="4" t="s">
+        <v>241</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>242</v>
+      </c>
+      <c r="D69" s="4" t="s">
+        <v>243</v>
+      </c>
+      <c r="E69" s="5"/>
+      <c r="F69" s="5"/>
+      <c r="H69" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I69" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J69" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K69" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L69" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M69" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N69" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q69" s="11"/>
+    </row>
+    <row r="70" ht="15.75" customHeight="1">
+      <c r="A70" s="4">
+        <v>69.0</v>
+      </c>
+      <c r="B70" s="4" t="s">
+        <v>244</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>245</v>
+      </c>
+      <c r="D70" s="4" t="s">
+        <v>246</v>
+      </c>
+      <c r="E70" s="5"/>
+      <c r="F70" s="5"/>
+      <c r="H70" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I70" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J70" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K70" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L70" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M70" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N70" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q70" s="11"/>
+    </row>
+    <row r="71" ht="15.75" customHeight="1">
+      <c r="A71" s="4">
+        <v>70.0</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>248</v>
+      </c>
+      <c r="D71" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="E71" s="5"/>
+      <c r="F71" s="5"/>
+      <c r="H71" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I71" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J71" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K71" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L71" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="M71" s="10" t="s">
+        <v>63</v>
+      </c>
+      <c r="N71" s="7" t="s">
+        <v>250</v>
+      </c>
+      <c r="Q71" s="11"/>
+    </row>
+    <row r="72" ht="15.75" customHeight="1">
+      <c r="A72" s="4">
+        <v>71.0</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>251</v>
+      </c>
+      <c r="C72" s="7" t="s">
+        <v>252</v>
+      </c>
+      <c r="D72" s="4" t="s">
+        <v>253</v>
+      </c>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="H72" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I72" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J72" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K72" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L72" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M72" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="N72" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q72" s="11"/>
+    </row>
+    <row r="73" ht="15.75" customHeight="1">
+      <c r="A73" s="4">
+        <v>72.0</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>255</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="D73" s="4" t="s">
+        <v>257</v>
+      </c>
+      <c r="E73" s="5"/>
+      <c r="F73" s="5"/>
+      <c r="H73" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I73" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J73" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K73" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L73" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M73" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N73" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q73" s="11"/>
+    </row>
+    <row r="74" ht="15.75" customHeight="1">
+      <c r="A74" s="4">
+        <v>73.0</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>259</v>
+      </c>
+      <c r="D74" s="4" t="s">
+        <v>260</v>
+      </c>
+      <c r="E74" s="5"/>
+      <c r="F74" s="5"/>
+      <c r="H74" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I74" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J74" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K74" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L74" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M74" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N74" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q74" s="11"/>
+    </row>
+    <row r="75" ht="15.75" customHeight="1">
+      <c r="A75" s="4">
+        <v>74.0</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>261</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>262</v>
+      </c>
+      <c r="D75" s="4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E75" s="5"/>
+      <c r="F75" s="5"/>
+      <c r="H75" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J75" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L75" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M75" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N75" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q75" s="11"/>
+    </row>
+    <row r="76" ht="15.75" customHeight="1">
+      <c r="A76" s="4">
+        <v>75.0</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="C76" s="12" t="s">
+        <v>265</v>
+      </c>
+      <c r="D76" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="H76" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J76" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L76" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="M76" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="N76" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q76" s="11"/>
+    </row>
+    <row r="77" ht="15.75" customHeight="1">
+      <c r="A77" s="4">
+        <v>76.0</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>267</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>268</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E77" s="5"/>
+      <c r="F77" s="5"/>
+      <c r="H77" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J77" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L77" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M77" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N77" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q77" s="11"/>
+    </row>
+    <row r="78" ht="15.75" customHeight="1">
+      <c r="A78" s="4">
+        <v>77.0</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>270</v>
+      </c>
+      <c r="C78" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E59" s="3"/>
-      <c r="F59" s="3"/>
-      <c r="H59" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I59" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J59" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K59" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L59" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M59" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="3">
-        <v>59.0</v>
-      </c>
-      <c r="B60" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="C60" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="D60" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="E60" s="3"/>
-      <c r="F60" s="3"/>
-      <c r="H60" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I60" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J60" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K60" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L60" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M60" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="3">
-        <v>60.0</v>
-      </c>
-      <c r="B61" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="C61" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="D61" s="3" t="s">
-        <v>206</v>
-      </c>
-      <c r="E61" s="3"/>
-      <c r="F61" s="3"/>
-      <c r="H61" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I61" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J61" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K61" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L61" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M61" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="3">
-        <v>61.0</v>
-      </c>
-      <c r="B62" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="C62" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="D62" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="H62" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I62" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J62" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K62" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L62" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M62" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="3">
-        <v>62.0</v>
-      </c>
-      <c r="B63" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="C63" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="D63" s="3" t="s">
-        <v>212</v>
-      </c>
-      <c r="E63" s="3"/>
-      <c r="F63" s="3"/>
-      <c r="H63" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I63" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J63" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K63" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L63" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M63" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="3">
-        <v>63.0</v>
-      </c>
-      <c r="B64" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="C64" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="D64" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="E64" s="3"/>
-      <c r="F64" s="3"/>
-      <c r="H64" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I64" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J64" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K64" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L64" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M64" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="3">
-        <v>64.0</v>
-      </c>
-      <c r="B65" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="C65" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="D65" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="E65" s="3"/>
-      <c r="F65" s="3"/>
-      <c r="H65" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I65" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J65" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K65" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L65" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M65" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="3">
-        <v>65.0</v>
-      </c>
-      <c r="B66" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C66" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="E66" s="3"/>
-      <c r="F66" s="3"/>
-      <c r="H66" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I66" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J66" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L66" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M66" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="3">
-        <v>66.0</v>
-      </c>
-      <c r="B67" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="C67" s="3" t="s">
-        <v>223</v>
-      </c>
-      <c r="D67" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="E67" s="3"/>
-      <c r="F67" s="3"/>
-      <c r="H67" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I67" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J67" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K67" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L67" s="3" t="s">
-        <v>146</v>
-      </c>
-      <c r="M67" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="3">
-        <v>67.0</v>
-      </c>
-      <c r="B68" s="3" t="s">
-        <v>226</v>
-      </c>
-      <c r="C68" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="D68" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="E68" s="3"/>
-      <c r="F68" s="3"/>
-      <c r="H68" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I68" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J68" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K68" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M68" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="3">
-        <v>68.0</v>
-      </c>
-      <c r="B69" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="C69" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="D69" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="E69" s="3"/>
-      <c r="F69" s="3"/>
-      <c r="H69" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I69" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J69" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K69" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L69" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M69" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="3">
-        <v>69.0</v>
-      </c>
-      <c r="B70" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="C70" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="D70" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="E70" s="3"/>
-      <c r="F70" s="3"/>
-      <c r="H70" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I70" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J70" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K70" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L70" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M70" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="3">
-        <v>70.0</v>
-      </c>
-      <c r="B71" s="3" t="s">
-        <v>235</v>
-      </c>
-      <c r="C71" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D71" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="H71" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I71" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J71" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K71" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M71" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="3">
-        <v>71.0</v>
-      </c>
-      <c r="B72" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="C72" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="D72" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="E72" s="3"/>
-      <c r="F72" s="3"/>
-      <c r="H72" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I72" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J72" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K72" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M72" s="4" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="3">
-        <v>72.0</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C73" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="D73" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="H73" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I73" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J73" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M73" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="3">
-        <v>73.0</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="E74" s="3"/>
-      <c r="F74" s="3"/>
-      <c r="H74" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I74" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J74" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K74" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M74" s="4" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="3">
-        <v>74.0</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>249</v>
-      </c>
-      <c r="E75" s="3"/>
-      <c r="F75" s="3"/>
-      <c r="H75" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I75" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J75" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K75" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L75" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M75" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="3">
-        <v>75.0</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="H76" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I76" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J76" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K76" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L76" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M76" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="3">
-        <v>76.0</v>
-      </c>
-      <c r="B77" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="C77" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="D77" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="E77" s="3"/>
-      <c r="F77" s="3"/>
-      <c r="H77" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I77" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J77" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K77" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L77" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M77" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="3">
-        <v>77.0</v>
-      </c>
-      <c r="B78" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="C78" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="D78" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="E78" s="3"/>
-      <c r="F78" s="3"/>
-      <c r="H78" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I78" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J78" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K78" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L78" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M78" s="4" t="s">
-        <v>225</v>
-      </c>
+      <c r="D78" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="E78" s="5"/>
+      <c r="F78" s="5"/>
+      <c r="H78" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J78" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M78" s="9" t="s">
+        <v>35</v>
+      </c>
+      <c r="N78" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q78" s="11"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="3">
+      <c r="A79" s="4">
         <v>78.0</v>
       </c>
-      <c r="B79" s="3" t="s">
-        <v>258</v>
-      </c>
-      <c r="C79" s="3" t="s">
-        <v>259</v>
-      </c>
-      <c r="D79" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="E79" s="3"/>
-      <c r="F79" s="3"/>
-      <c r="H79" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I79" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J79" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K79" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L79" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="M79" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="B79" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>274</v>
+      </c>
+      <c r="E79" s="5"/>
+      <c r="F79" s="5"/>
+      <c r="H79" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J79" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L79" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M79" s="8" t="s">
+        <v>63</v>
+      </c>
+      <c r="N79" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q79" s="11"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="3">
+      <c r="A80" s="4">
         <v>79.0</v>
       </c>
-      <c r="B80" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="C80" s="3" t="s">
-        <v>262</v>
-      </c>
-      <c r="D80" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="H80" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I80" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J80" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K80" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L80" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M80" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="B80" s="4" t="s">
+        <v>275</v>
+      </c>
+      <c r="C80" s="7" t="s">
+        <v>276</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>277</v>
+      </c>
+      <c r="E80" s="5"/>
+      <c r="F80" s="5"/>
+      <c r="H80" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J80" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L80" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M80" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N80" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q80" s="11"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="3">
+      <c r="A81" s="4">
         <v>80.0</v>
       </c>
-      <c r="B81" s="3" t="s">
-        <v>264</v>
-      </c>
-      <c r="C81" s="3" t="s">
-        <v>265</v>
-      </c>
-      <c r="D81" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="H81" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I81" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J81" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K81" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L81" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M81" s="4" t="s">
-        <v>20</v>
-      </c>
+      <c r="B81" s="4" t="s">
+        <v>278</v>
+      </c>
+      <c r="C81" s="7" t="s">
+        <v>279</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>280</v>
+      </c>
+      <c r="E81" s="5"/>
+      <c r="F81" s="5"/>
+      <c r="H81" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J81" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L81" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M81" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N81" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q81" s="11"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="3">
+      <c r="A82" s="4">
         <v>81.0</v>
       </c>
-      <c r="B82" s="3" t="s">
-        <v>267</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>268</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="E82" s="3"/>
-      <c r="F82" s="3"/>
-      <c r="H82" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="I82" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="J82" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="K82" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="L82" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="M82" s="4" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="83" ht="15.75" customHeight="1"/>
-    <row r="84" ht="15.75" customHeight="1"/>
-    <row r="85" ht="15.75" customHeight="1"/>
-    <row r="86" ht="15.75" customHeight="1"/>
-    <row r="87" ht="15.75" customHeight="1"/>
-    <row r="88" ht="15.75" customHeight="1"/>
-    <row r="89" ht="15.75" customHeight="1"/>
-    <row r="90" ht="15.75" customHeight="1"/>
-    <row r="91" ht="15.75" customHeight="1"/>
-    <row r="92" ht="15.75" customHeight="1"/>
-    <row r="93" ht="15.75" customHeight="1"/>
-    <row r="94" ht="15.75" customHeight="1"/>
-    <row r="95" ht="15.75" customHeight="1"/>
-    <row r="96" ht="15.75" customHeight="1"/>
-    <row r="97" ht="15.75" customHeight="1"/>
-    <row r="98" ht="15.75" customHeight="1"/>
-    <row r="99" ht="15.75" customHeight="1"/>
-    <row r="100" ht="15.75" customHeight="1"/>
-    <row r="101" ht="15.75" customHeight="1"/>
-    <row r="102" ht="15.75" customHeight="1"/>
-    <row r="103" ht="15.75" customHeight="1"/>
-    <row r="104" ht="15.75" customHeight="1"/>
-    <row r="105" ht="15.75" customHeight="1"/>
-    <row r="106" ht="15.75" customHeight="1"/>
-    <row r="107" ht="15.75" customHeight="1"/>
-    <row r="108" ht="15.75" customHeight="1"/>
-    <row r="109" ht="15.75" customHeight="1"/>
+      <c r="B82" s="13" t="s">
+        <v>281</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>282</v>
+      </c>
+      <c r="D82" s="4" t="s">
+        <v>283</v>
+      </c>
+      <c r="E82" s="5"/>
+      <c r="F82" s="5"/>
+      <c r="H82" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="J82" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="L82" s="9" t="s">
+        <v>34</v>
+      </c>
+      <c r="M82" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="N82" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="Q82" s="11"/>
+    </row>
+    <row r="83" ht="15.75" customHeight="1">
+      <c r="Q83" s="11"/>
+    </row>
+    <row r="84" ht="15.75" customHeight="1">
+      <c r="Q84" s="11"/>
+    </row>
+    <row r="85" ht="15.75" customHeight="1">
+      <c r="Q85" s="11"/>
+    </row>
+    <row r="86" ht="15.75" customHeight="1">
+      <c r="Q86" s="11"/>
+    </row>
+    <row r="87" ht="15.75" customHeight="1">
+      <c r="Q87" s="11"/>
+    </row>
+    <row r="88" ht="15.75" customHeight="1">
+      <c r="Q88" s="11"/>
+    </row>
+    <row r="89" ht="15.75" customHeight="1">
+      <c r="Q89" s="11"/>
+    </row>
+    <row r="90" ht="15.75" customHeight="1">
+      <c r="Q90" s="11"/>
+    </row>
+    <row r="91" ht="15.75" customHeight="1">
+      <c r="Q91" s="11"/>
+    </row>
+    <row r="92" ht="15.75" customHeight="1">
+      <c r="Q92" s="11"/>
+    </row>
+    <row r="93" ht="15.75" customHeight="1">
+      <c r="Q93" s="11"/>
+    </row>
+    <row r="94" ht="15.75" customHeight="1">
+      <c r="Q94" s="11"/>
+    </row>
+    <row r="95" ht="15.75" customHeight="1">
+      <c r="Q95" s="11"/>
+    </row>
+    <row r="96" ht="15.75" customHeight="1">
+      <c r="Q96" s="11"/>
+    </row>
+    <row r="97" ht="15.75" customHeight="1">
+      <c r="Q97" s="11"/>
+    </row>
+    <row r="98" ht="15.75" customHeight="1">
+      <c r="Q98" s="11"/>
+    </row>
+    <row r="99" ht="15.75" customHeight="1">
+      <c r="Q99" s="11"/>
+    </row>
+    <row r="100" ht="15.75" customHeight="1">
+      <c r="Q100" s="11"/>
+    </row>
+    <row r="101" ht="15.75" customHeight="1">
+      <c r="Q101" s="11"/>
+    </row>
+    <row r="102" ht="15.75" customHeight="1">
+      <c r="Q102" s="11"/>
+    </row>
+    <row r="103" ht="15.75" customHeight="1">
+      <c r="Q103" s="11"/>
+    </row>
+    <row r="104" ht="15.75" customHeight="1">
+      <c r="Q104" s="11"/>
+    </row>
+    <row r="105" ht="15.75" customHeight="1">
+      <c r="Q105" s="11"/>
+    </row>
+    <row r="106" ht="15.75" customHeight="1">
+      <c r="Q106" s="11"/>
+    </row>
+    <row r="107" ht="15.75" customHeight="1">
+      <c r="Q107" s="11"/>
+    </row>
+    <row r="108" ht="15.75" customHeight="1">
+      <c r="Q108" s="11"/>
+    </row>
+    <row r="109" ht="15.75" customHeight="1">
+      <c r="Q109" s="11"/>
+    </row>
     <row r="110" ht="15.75" customHeight="1"/>
     <row r="111" ht="15.75" customHeight="1"/>
     <row r="112" ht="15.75" customHeight="1"/>
@@ -5275,6 +5776,9 @@
   <pageMargins bottom="1.0" footer="0.0" header="0.0" left="0.75" right="0.75" top="1.0"/>
   <pageSetup orientation="landscape"/>
   <drawing r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId3"/>
+  </tableParts>
 </worksheet>
 </file>
 
@@ -5290,68 +5794,68 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="s">
-        <v>270</v>
+      <c r="A1" s="1" t="s">
+        <v>0</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="s">
-        <v>271</v>
+      <c r="A2" s="1" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="s">
-        <v>272</v>
+      <c r="A4" s="1" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>273</v>
+      <c r="A5" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="s">
-        <v>274</v>
+      <c r="A7" s="1" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="s">
-        <v>275</v>
+      <c r="A8" s="1" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="s">
-        <v>276</v>
+      <c r="A9" s="1" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="s">
-        <v>277</v>
+      <c r="A10" s="1" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="s">
-        <v>278</v>
+      <c r="A11" s="1" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="s">
-        <v>279</v>
+      <c r="A12" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="s">
-        <v>280</v>
+      <c r="A14" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="s">
-        <v>281</v>
+      <c r="A15" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="s">
-        <v>282</v>
+      <c r="A16" s="1" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>
